--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1421,6 +1421,542 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129298362</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 46824, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566785</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6400923</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129298333</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98669</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 46824, Östantorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566786</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6400920</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129301003</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92826</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 46824, Östantorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566758</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6400899</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Missade att ta exakta koordinater</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129298391</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92862</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>A 46824, Östantorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566683</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6400894</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129298551</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58095</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>A 46824, Östantorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566714</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6400893</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129298551</v>
       </c>
       <c r="B12" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92871</v>
+        <v>92899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129298551</v>
       </c>
       <c r="B12" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92899</v>
+        <v>92905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129298551</v>
       </c>
       <c r="B12" t="n">
-        <v>58100</v>
+        <v>58105</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -1426,7 +1426,7 @@
         <v>129298362</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>129298333</v>
       </c>
       <c r="B9" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         <v>129301003</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>129298391</v>
       </c>
       <c r="B11" t="n">
-        <v>92905</v>
+        <v>92906</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>129298551</v>
       </c>
       <c r="B12" t="n">
-        <v>58105</v>
+        <v>58106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>98556872</v>
+        <v>129301003</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 5529, Hagen, Östantorp, Sm</t>
+          <t>A 46824, Östantorp, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566755.1871885459</v>
+        <v>566758</v>
       </c>
       <c r="R2" t="n">
-        <v>6400916.701640934</v>
+        <v>6400899</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,27 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridda och säkert 20-tal fröställningar. Bladen svåra att se i den djupa mossan.</t>
+          <t>Missade att ta exakta koordinater</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,65 +789,59 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98557238</v>
+        <v>129298391</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5964</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 5529, Hagen, Östantorp, Sm</t>
+          <t>A 46824, Östantorp, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566802.9617465938</v>
+        <v>566683</v>
       </c>
       <c r="R3" t="n">
-        <v>6400906.282389451</v>
+        <v>6400894</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,27 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flera fröställningar</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>98556894</v>
+        <v>98556872</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,7 +926,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -983,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566753.1985492596</v>
+        <v>566755</v>
       </c>
       <c r="R4" t="n">
-        <v>6400907.593625175</v>
+        <v>6400917</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,19 +978,14 @@
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spridda och säkert 20-tal fröställningar. Bladen svåra att se i den djupa mossan.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98557202</v>
+        <v>98556885</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,7 +1041,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1104,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566759.3012201074</v>
+        <v>566766</v>
       </c>
       <c r="R5" t="n">
-        <v>6400894.348887235</v>
+        <v>6400910</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1137,19 +1093,9 @@
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1177,15 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>98556950</v>
+        <v>98556894</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1225,10 +1166,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566742.0226814578</v>
+        <v>566753</v>
       </c>
       <c r="R6" t="n">
-        <v>6400904.205656492</v>
+        <v>6400908</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,19 +1199,9 @@
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1298,15 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>98556885</v>
+        <v>98556950</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,11 +1257,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1350,10 +1272,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>566765.9873576153</v>
+        <v>566742</v>
       </c>
       <c r="R7" t="n">
-        <v>6400910.474498686</v>
+        <v>6400904</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1383,19 +1305,9 @@
           <t>2022-02-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-02-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1423,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129298362</v>
+        <v>98557202</v>
       </c>
       <c r="B8" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,14 +1374,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 46824, Sm</t>
+          <t>A 5529, Hagen, Östantorp, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>566785</v>
+        <v>566759</v>
       </c>
       <c r="R8" t="n">
-        <v>6400923</v>
+        <v>6400894</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1496,12 +1408,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1529,10 +1441,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129298333</v>
+        <v>98557238</v>
       </c>
       <c r="B9" t="n">
-        <v>98769</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1557,7 +1469,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1568,14 +1484,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 46824, Östantorp, Sm</t>
+          <t>A 5529, Hagen, Östantorp, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>566786</v>
+        <v>566803</v>
       </c>
       <c r="R9" t="n">
-        <v>6400920</v>
+        <v>6400906</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,12 +1518,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2022-02-10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera fröställningar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,45 +1556,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129301003</v>
+        <v>129298333</v>
       </c>
       <c r="B10" t="n">
-        <v>92870</v>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1681,13 +1599,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>566758</v>
+        <v>566786</v>
       </c>
       <c r="R10" t="n">
-        <v>6400899</v>
+        <v>6400920</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1717,11 +1635,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Missade att ta exakta koordinater</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,59 +1662,56 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129298391</v>
+        <v>129298362</v>
       </c>
       <c r="B11" t="n">
-        <v>92906</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5964</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>A 46824, Östantorp, Sm</t>
+          <t>A 46824, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>566683</v>
+        <v>566785</v>
       </c>
       <c r="R11" t="n">
-        <v>6400894</v>
+        <v>6400923</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1855,107 +1765,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>129298551</v>
-      </c>
-      <c r="B12" t="n">
-        <v>58106</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>A 46824, Östantorp, Sm</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>566714</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6400893</v>
-      </c>
-      <c r="S12" t="n">
-        <v>100</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Vimmerby</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Locknevi</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-10-23</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Magnus Kasselstrand</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46824-2025 artfynd.xlsx
+++ b/artfynd/A 46824-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129301003</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129298391</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98556872</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98556885</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98556894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98556950</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98557202</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98557238</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1659,6 +1704,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129298333</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1765,8 +1815,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129298362</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>